--- a/data/trans_bre/P29A_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P29A_R-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-30,82; -15,04</t>
+          <t>-31,6; -15,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-30,64; -12,84</t>
+          <t>-31,29; -13,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-32,73; -16,19</t>
+          <t>-32,6; -16,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-34,49; -17,5</t>
+          <t>-34,34; -17,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-56,33; -31,75</t>
+          <t>-57,94; -31,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-51,49; -24,37</t>
+          <t>-52,08; -26,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-51,44; -29,28</t>
+          <t>-51,96; -29,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-54,57; -34,34</t>
+          <t>-54,52; -33,74</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-36,29; -25,41</t>
+          <t>-36,42; -25,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-39,12; -26,68</t>
+          <t>-39,46; -26,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-38,7; -27,9</t>
+          <t>-40,16; -28,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-34,08; -20,37</t>
+          <t>-33,19; -19,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-79,87; -65,38</t>
+          <t>-79,31; -64,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-65,14; -49,32</t>
+          <t>-65,48; -49,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-71,84; -57,48</t>
+          <t>-72,26; -57,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-62,69; -45,46</t>
+          <t>-61,64; -43,2</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-41,13; -27,39</t>
+          <t>-40,97; -25,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-33,18; -17,29</t>
+          <t>-32,96; -16,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-34,82; -20,2</t>
+          <t>-34,22; -18,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-40,02; -26,36</t>
+          <t>-39,13; -25,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-65,76; -48,4</t>
+          <t>-66,11; -47,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-53,96; -31,53</t>
+          <t>-53,31; -31,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-53,3; -34,44</t>
+          <t>-52,84; -32,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-64,32; -47,66</t>
+          <t>-63,62; -46,69</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-37,33; -23,55</t>
+          <t>-37,22; -23,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-35,12; -21,15</t>
+          <t>-34,61; -21,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-30,82; -15,7</t>
+          <t>-30,44; -16,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-43,72; -20,94</t>
+          <t>-43,22; -20,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,79; -37,78</t>
+          <t>-55,06; -38,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,58; -49,69</t>
+          <t>-68,75; -48,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,56; -28,84</t>
+          <t>-49,02; -29,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-72,13; -39,91</t>
+          <t>-70,61; -39,25</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-33,05; -15,47</t>
+          <t>-32,48; -15,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-44,42; -26,74</t>
+          <t>-44,45; -26,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-32,32; -15,61</t>
+          <t>-32,11; -15,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,72; -8,34</t>
+          <t>-19,62; -8,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-70,36; -39,44</t>
+          <t>-70,44; -40,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-72,92; -50,21</t>
+          <t>-71,35; -49,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-70,25; -41,32</t>
+          <t>-71,36; -42,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-87,01; -55,56</t>
+          <t>-87,07; -55,8</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,92; -23,11</t>
+          <t>-39,62; -23,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-43,88; -27,5</t>
+          <t>-43,75; -27,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-40,78; -24,78</t>
+          <t>-41,42; -24,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-30,81; -16,38</t>
+          <t>-30,99; -16,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-53,48; -34,4</t>
+          <t>-54,2; -35,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-63,6; -44,77</t>
+          <t>-63,15; -44,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-54,97; -37,03</t>
+          <t>-56,39; -37,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-47,44; -28,14</t>
+          <t>-48,13; -28,93</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-30,13; -19,53</t>
+          <t>-30,45; -19,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-35,17; -23,66</t>
+          <t>-35,19; -23,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-27,28; -15,78</t>
+          <t>-26,66; -15,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,66; 26,18</t>
+          <t>-20,67; 26,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-63,32; -46,47</t>
+          <t>-63,77; -47,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-58,75; -44,21</t>
+          <t>-58,99; -44,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-45,09; -28,98</t>
+          <t>-44,4; -27,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-40,81; 56,27</t>
+          <t>-40,99; 55,0</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-41,0; -31,68</t>
+          <t>-40,81; -31,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,96; -26,83</t>
+          <t>-36,65; -26,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-31,12; -21,52</t>
+          <t>-31,22; -21,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-28,5; 2,34</t>
+          <t>-28,16; 0,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-62,45; -51,58</t>
+          <t>-62,12; -51,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-64,39; -51,63</t>
+          <t>-64,37; -51,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-53,35; -40,08</t>
+          <t>-53,07; -39,4</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-68,5; 14,61</t>
+          <t>-67,58; -1,25</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-32,71; -28,28</t>
+          <t>-32,58; -27,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-32,76; -27,95</t>
+          <t>-32,8; -28,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-28,68; -23,9</t>
+          <t>-28,88; -23,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-24,43; -1,38</t>
+          <t>-24,35; -3,41</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-58,35; -52,46</t>
+          <t>-58,29; -52,1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-57,11; -50,79</t>
+          <t>-57,27; -51,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-49,13; -42,69</t>
+          <t>-49,35; -42,69</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-50,25; -2,74</t>
+          <t>-50,72; -7,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P29A_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P29A_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-26,45</t>
+          <t>-22,52</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-45,79%</t>
+          <t>-42,27%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-31,6; -15,08</t>
+          <t>-32,04; -15,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-31,29; -13,81</t>
+          <t>-30,8; -13,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-32,6; -16,26</t>
+          <t>-33,02; -16,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-34,34; -17,39</t>
+          <t>-29,67; -15,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-57,94; -31,33</t>
+          <t>-58,04; -31,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-52,08; -26,41</t>
+          <t>-51,36; -26,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-51,96; -29,28</t>
+          <t>-52,16; -29,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-54,52; -33,74</t>
+          <t>-51,13; -30,71</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-26,78</t>
+          <t>-26,67</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-54,08%</t>
+          <t>-54,23%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-36,42; -25,67</t>
+          <t>-36,53; -25,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-39,46; -26,97</t>
+          <t>-40,49; -27,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-40,16; -28,39</t>
+          <t>-39,52; -28,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-33,19; -19,2</t>
+          <t>-32,83; -20,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-79,31; -64,69</t>
+          <t>-79,37; -63,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-65,48; -49,8</t>
+          <t>-65,8; -50,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-72,26; -57,31</t>
+          <t>-71,67; -56,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-61,64; -43,2</t>
+          <t>-61,58; -45,39</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-32,84</t>
+          <t>-34,34</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-56,04%</t>
+          <t>-57,92%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-40,97; -25,97</t>
+          <t>-41,42; -26,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-32,96; -16,84</t>
+          <t>-32,52; -16,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-34,22; -18,92</t>
+          <t>-34,95; -19,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-39,13; -25,52</t>
+          <t>-41,23; -27,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-66,11; -47,66</t>
+          <t>-66,57; -49,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-53,31; -31,09</t>
+          <t>-53,83; -31,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-52,84; -32,95</t>
+          <t>-53,44; -32,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-63,62; -46,69</t>
+          <t>-65,36; -49,89</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-30,87</t>
+          <t>-21,73</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-54,15%</t>
+          <t>-39,85%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-37,22; -23,75</t>
+          <t>-37,25; -23,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-34,61; -21,08</t>
+          <t>-34,89; -21,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-30,44; -16,65</t>
+          <t>-30,53; -15,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-43,22; -20,99</t>
+          <t>-30,23; -13,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,06; -38,29</t>
+          <t>-54,41; -38,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-68,75; -48,9</t>
+          <t>-68,73; -49,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,02; -29,29</t>
+          <t>-48,68; -28,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-70,61; -39,25</t>
+          <t>-50,55; -27,71</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-13,31</t>
+          <t>-11,83</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-76,39%</t>
+          <t>-71,25%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-32,48; -15,4</t>
+          <t>-33,05; -14,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-44,45; -26,39</t>
+          <t>-44,19; -26,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-32,11; -15,87</t>
+          <t>-32,5; -16,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,62; -8,29</t>
+          <t>-17,35; -6,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-70,44; -40,24</t>
+          <t>-70,56; -39,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-71,35; -49,23</t>
+          <t>-71,64; -49,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-71,36; -42,49</t>
+          <t>-70,5; -43,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-87,07; -55,8</t>
+          <t>-84,05; -49,13</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-23,82</t>
+          <t>-23,08</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-38,84%</t>
+          <t>-38,27%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-39,62; -23,78</t>
+          <t>-39,74; -24,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-43,75; -27,75</t>
+          <t>-44,41; -27,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-41,42; -24,56</t>
+          <t>-40,57; -24,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-30,99; -16,74</t>
+          <t>-30,18; -16,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-54,2; -35,47</t>
+          <t>-54,1; -35,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-63,15; -44,4</t>
+          <t>-64,16; -45,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-56,39; -37,17</t>
+          <t>-55,5; -37,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-48,13; -28,93</t>
+          <t>-47,97; -28,77</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-2,11</t>
+          <t>-18,24</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-4,26%</t>
+          <t>-37,18%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-30,45; -19,51</t>
+          <t>-30,78; -19,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-35,19; -23,89</t>
+          <t>-34,42; -23,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-26,66; -15,06</t>
+          <t>-26,62; -15,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,67; 26,12</t>
+          <t>-23,63; -13,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-63,77; -47,27</t>
+          <t>-64,33; -47,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-58,99; -44,18</t>
+          <t>-58,6; -44,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-44,4; -27,65</t>
+          <t>-43,82; -28,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-40,99; 55,0</t>
+          <t>-45,17; -28,2</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-15,88</t>
+          <t>-25,5</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-53,15%</t>
+          <t>-64,75%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-40,81; -31,57</t>
+          <t>-40,77; -31,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,65; -26,67</t>
+          <t>-36,44; -26,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-31,22; -21,22</t>
+          <t>-31,15; -20,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-28,16; 0,18</t>
+          <t>-29,69; -20,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-62,12; -51,08</t>
+          <t>-62,17; -50,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-64,37; -51,28</t>
+          <t>-64,23; -51,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-53,07; -39,4</t>
+          <t>-53,46; -39,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-67,58; -1,25</t>
+          <t>-70,89; -57,33</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-17,61</t>
+          <t>-23,37</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-38,49%</t>
+          <t>-48,96%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-32,58; -27,95</t>
+          <t>-32,84; -28,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-32,8; -28,13</t>
+          <t>-32,73; -28,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-28,88; -23,99</t>
+          <t>-28,87; -23,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-24,35; -3,41</t>
+          <t>-25,36; -20,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-58,29; -52,1</t>
+          <t>-58,51; -52,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-57,27; -51,17</t>
+          <t>-56,98; -50,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-49,35; -42,69</t>
+          <t>-49,33; -42,84</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-50,72; -7,52</t>
+          <t>-51,99; -45,27</t>
         </is>
       </c>
     </row>
